--- a/program.xlsx
+++ b/program.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdf8079a848cfec2/MyFiles/Courses/MasterBiotechnologieSante_FSTetouan/00_Info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{254268C7-1D32-4852-9976-A10E8A9A7E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3664F2C-01C8-498D-887A-9B7F04D3E42B}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{254268C7-1D32-4852-9976-A10E8A9A7E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F3C8762-61F8-4542-ACCC-C2960BB9A7A6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{C0FD0F4E-51C4-4199-A0DC-2019CC4F564A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{C0FD0F4E-51C4-4199-A0DC-2019CC4F564A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Program" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,45 +36,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
-  <si>
-    <t>welcome</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+  <si>
+    <t>Welcome</t>
+  </si>
+  <si>
+    <t>Presentation</t>
+  </si>
+  <si>
+    <t>HPC+Git</t>
+  </si>
+  <si>
+    <t>Practical</t>
   </si>
   <si>
     <t>HPC</t>
   </si>
   <si>
+    <t>Introduction to scRNA</t>
+  </si>
+  <si>
+    <t>Discussion</t>
+  </si>
+  <si>
     <t>NGS</t>
   </si>
   <si>
-    <t>database</t>
-  </si>
-  <si>
-    <t>Qualtiy</t>
-  </si>
-  <si>
-    <t>FastAC</t>
-  </si>
-  <si>
-    <t>triming</t>
-  </si>
-  <si>
-    <t>Welcome</t>
+    <t>QC</t>
+  </si>
+  <si>
+    <t>Pause</t>
   </si>
   <si>
     <t>Dabases</t>
   </si>
   <si>
-    <t>HPC+Git</t>
-  </si>
-  <si>
-    <t>Presentation</t>
-  </si>
-  <si>
-    <t>Practical</t>
-  </si>
-  <si>
-    <t>Pause</t>
+    <t>QC report Illumina NP</t>
   </si>
   <si>
     <t>FastQC</t>
@@ -84,7 +80,7 @@
     <t>Triming</t>
   </si>
   <si>
-    <t>QC report Illumina NP</t>
+    <t xml:space="preserve">Triming </t>
   </si>
   <si>
     <t>VC introduction</t>
@@ -97,12 +93,6 @@
   </si>
   <si>
     <t>Alignment SAM</t>
-  </si>
-  <si>
-    <t>Discussion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triming </t>
   </si>
   <si>
     <t>Aggregating QC metrics using MultiQC</t>
@@ -119,9 +109,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,7 +172,7 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -191,7 +181,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -522,385 +512,577 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61EA5EA-8461-4B9C-9F72-AF14412E8E47}">
-  <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874694C3-6C34-41C1-BAFA-5CBF17469AFF}">
+  <dimension ref="C3:L33"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="8.7265625" style="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="6" max="6" width="39" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>15</v>
-      </c>
-      <c r="D2">
-        <f>SUM(C2:C5)</f>
-        <v>105</v>
-      </c>
-      <c r="E2" s="1">
-        <f>TIME(,D2,)</f>
-        <v>7.2916666666666671E-2</v>
-      </c>
-      <c r="F2" s="1">
-        <f>SUM(E2:E9)</f>
-        <v>0.14583333333333334</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="H2" s="1">
-        <f>F2+G2</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>30</v>
-      </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>30</v>
-      </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C6"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-      <c r="D7">
-        <f>SUM(C7:C10)</f>
-        <v>105</v>
-      </c>
-      <c r="E7" s="1">
-        <f>TIME(,D7,)</f>
-        <v>7.2916666666666671E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9">
-        <v>45</v>
-      </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C10" s="1">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874694C3-6C34-41C1-BAFA-5CBF17469AFF}">
-  <dimension ref="C3:L33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:12">
+      <c r="D3" s="2">
+        <v>0.36458333333333331</v>
+      </c>
       <c r="E3" s="2">
         <v>0.35416666666666669</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="3:12">
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.375</v>
       </c>
       <c r="E4" s="2">
         <v>0.36458333333333331</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12">
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.38541666666666702</v>
       </c>
       <c r="E5" s="2">
         <v>0.375</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.38541666666666702</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12">
       <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.39583333333333298</v>
       </c>
       <c r="E6" s="2">
         <v>0.38541666666666702</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.38541666666666702</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12">
       <c r="C7" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.40625</v>
       </c>
       <c r="E7" s="2">
         <v>0.39583333333333298</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.40625</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="3:12">
+      <c r="D8" s="2">
+        <v>0.41666666666666602</v>
+      </c>
       <c r="E8" s="2">
         <v>0.40625</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.41666666666666602</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.40625</v>
+      </c>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="3:12">
+      <c r="D9" s="2">
+        <v>0.42708333333333298</v>
+      </c>
       <c r="E9" s="2">
         <v>0.41666666666666602</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.42708333333333298</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.41666666666666602</v>
+      </c>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="3:12">
+      <c r="D10" s="2">
+        <v>0.4375</v>
+      </c>
       <c r="E10" s="2">
         <v>0.42708333333333298</v>
       </c>
       <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I10" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.42708333333333298</v>
+      </c>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="3:12">
+      <c r="D11" s="2">
+        <v>0.44791666666666602</v>
+      </c>
       <c r="E11" s="2">
         <v>0.4375</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I11" s="2">
+        <v>0.44791666666666602</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="3:12">
+      <c r="D12" s="2">
+        <v>0.45833333333333298</v>
+      </c>
       <c r="E12" s="2">
         <v>0.44791666666666602</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.44791666666666602</v>
+      </c>
+      <c r="K12" s="6"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:12">
+      <c r="D13" s="2">
+        <v>0.46875</v>
+      </c>
       <c r="E13" s="2">
         <v>0.45833333333333298</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.46875</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="3:12">
+      <c r="D14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
       <c r="E14" s="2">
         <v>0.46875</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.46875</v>
+      </c>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="3:12">
+      <c r="D15" s="2">
+        <v>0.48958333333333298</v>
+      </c>
       <c r="E15" s="2">
         <v>0.47916666666666702</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="3:12">
+      <c r="D16" s="2">
+        <v>0.5</v>
+      </c>
       <c r="E16" s="2">
         <v>0.48958333333333298</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.48958333333333298</v>
+      </c>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="4:11">
+      <c r="D17" s="2">
+        <v>0.51041666666666596</v>
+      </c>
       <c r="E17" s="2">
         <v>0.5</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="I17" s="2">
+        <v>0.51041666666666596</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="4:11">
+      <c r="D18" s="2">
+        <v>0.52083333333333304</v>
+      </c>
       <c r="E18" s="2">
         <v>0.51041666666666596</v>
       </c>
       <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="I18" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.51041666666666596</v>
+      </c>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="4:11">
+      <c r="D19" s="2">
+        <v>0.53125</v>
+      </c>
       <c r="E19" s="2">
         <v>0.52083333333333304</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="I19" s="2">
+        <v>0.53125</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.52083333333333304</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11">
+      <c r="D20" s="2">
+        <v>0.54166666666666596</v>
+      </c>
       <c r="E20" s="2">
         <v>0.53125</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="5:7" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.53125</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="4:11">
+      <c r="D21" s="2">
+        <v>0.55208333333333304</v>
+      </c>
       <c r="E21" s="2">
         <v>0.54166666666666596</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="5:7" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.55208333333333304</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.54166666666666596</v>
+      </c>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="4:11">
+      <c r="D22" s="2">
+        <v>0.5625</v>
+      </c>
       <c r="E22" s="2">
         <v>0.55208333333333304</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="5:7" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.55208333333333304</v>
+      </c>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="4:11">
+      <c r="D23" s="2">
+        <v>0.57291666666666596</v>
+      </c>
       <c r="E23" s="2">
         <v>0.5625</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="I23" s="2">
+        <v>0.57291666666666596</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="24" spans="4:11">
+      <c r="D24" s="2">
+        <v>0.58333333333333304</v>
+      </c>
       <c r="E24" s="2">
         <v>0.57291666666666596</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="I24" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0.57291666666666596</v>
+      </c>
+    </row>
+    <row r="25" spans="4:11">
+      <c r="D25" s="2">
+        <v>0.593749999999999</v>
+      </c>
       <c r="E25" s="2">
         <v>0.58333333333333304</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="I25" s="2">
+        <v>0.593749999999999</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="4:11">
+      <c r="D26" s="2">
+        <v>0.60416666666666596</v>
+      </c>
       <c r="E26" s="2">
         <v>0.593749999999999</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="I26" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0.593749999999999</v>
+      </c>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="4:11">
+      <c r="D27" s="2">
+        <v>0.61458333333333304</v>
+      </c>
       <c r="E27" s="2">
         <v>0.60416666666666596</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="5:7" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0.61458333333333304</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="4:11">
+      <c r="D28" s="2">
+        <v>0.624999999999999</v>
+      </c>
       <c r="E28" s="2">
         <v>0.61458333333333304</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="5:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0.624999999999999</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0.61458333333333304</v>
+      </c>
+      <c r="K28" s="6"/>
+    </row>
+    <row r="29" spans="4:11">
+      <c r="D29" s="2">
+        <v>0.63541666666666596</v>
+      </c>
       <c r="E29" s="2">
         <v>0.624999999999999</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="5:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0.63541666666666596</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0.624999999999999</v>
+      </c>
+      <c r="K29" s="6"/>
+    </row>
+    <row r="30" spans="4:11">
+      <c r="D30" s="2">
+        <v>0.64583333333333304</v>
+      </c>
       <c r="E30" s="2">
         <v>0.63541666666666596</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="5:7" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0.63541666666666596</v>
+      </c>
+      <c r="K30" s="6"/>
+    </row>
+    <row r="31" spans="4:11">
+      <c r="D31" s="2">
+        <v>0.656249999999999</v>
+      </c>
       <c r="E31" s="2">
         <v>0.64583333333333304</v>
       </c>
-    </row>
-    <row r="32" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="I31" s="2">
+        <v>0.656249999999999</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="K31" s="6"/>
+    </row>
+    <row r="32" spans="4:11">
+      <c r="D32" s="2">
+        <v>0.66666666666666596</v>
+      </c>
       <c r="E32" s="2">
         <v>0.656249999999999</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="5:7" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0.656249999999999</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="5:11">
       <c r="E33" s="2">
         <v>0.66666666666666596</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G33" s="2">
         <f>E33-E19</f>
         <v>0.14583333333333293</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/program.xlsx
+++ b/program.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdf8079a848cfec2/MyFiles/Courses/MasterBiotechnologieSante_FSTetouan/00_Info/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fdf8079a848cfec2/Yassine/Courses/MasterBiotechnologieSante_FSTetouan/00_Info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{254268C7-1D32-4852-9976-A10E8A9A7E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F3C8762-61F8-4542-ACCC-C2960BB9A7A6}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{254268C7-1D32-4852-9976-A10E8A9A7E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DC600D7-748B-4665-BCFE-DA48DE7F44D1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{C0FD0F4E-51C4-4199-A0DC-2019CC4F564A}"/>
+    <workbookView xWindow="25812" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C0FD0F4E-51C4-4199-A0DC-2019CC4F564A}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
   <si>
     <t>Welcome</t>
   </si>
@@ -102,6 +103,162 @@
   </si>
   <si>
     <t>Variant Calling</t>
+  </si>
+  <si>
+    <t>P1ssw0rd</t>
+  </si>
+  <si>
+    <t>strato01</t>
+  </si>
+  <si>
+    <t>strato02</t>
+  </si>
+  <si>
+    <t>strato03</t>
+  </si>
+  <si>
+    <t>strato04</t>
+  </si>
+  <si>
+    <t>strato05</t>
+  </si>
+  <si>
+    <t>strato06</t>
+  </si>
+  <si>
+    <t>strato07</t>
+  </si>
+  <si>
+    <t>strato08</t>
+  </si>
+  <si>
+    <t>strato09</t>
+  </si>
+  <si>
+    <t>strato10</t>
+  </si>
+  <si>
+    <t>strato11</t>
+  </si>
+  <si>
+    <t>strato12</t>
+  </si>
+  <si>
+    <t>strato13</t>
+  </si>
+  <si>
+    <t>strato14</t>
+  </si>
+  <si>
+    <t>cont01</t>
+  </si>
+  <si>
+    <t>cont02</t>
+  </si>
+  <si>
+    <t>cont03</t>
+  </si>
+  <si>
+    <t>cont04</t>
+  </si>
+  <si>
+    <t>cont05</t>
+  </si>
+  <si>
+    <t>cont06</t>
+  </si>
+  <si>
+    <t>cont07</t>
+  </si>
+  <si>
+    <t>cont08</t>
+  </si>
+  <si>
+    <t>cont09</t>
+  </si>
+  <si>
+    <t>cont10</t>
+  </si>
+  <si>
+    <t>cont11</t>
+  </si>
+  <si>
+    <t>cont12</t>
+  </si>
+  <si>
+    <t>Achtak</t>
+  </si>
+  <si>
+    <t>Hakik</t>
+  </si>
+  <si>
+    <t>khaldoune</t>
+  </si>
+  <si>
+    <t>BadrChair</t>
+  </si>
+  <si>
+    <t>Elouahabi</t>
+  </si>
+  <si>
+    <t>Habiba</t>
+  </si>
+  <si>
+    <t>Tahiri Hamza</t>
+  </si>
+  <si>
+    <t>Hasna</t>
+  </si>
+  <si>
+    <t>Aklouch</t>
+  </si>
+  <si>
+    <t>Mendil</t>
+  </si>
+  <si>
+    <t>Salmoun</t>
+  </si>
+  <si>
+    <t>El Biari</t>
+  </si>
+  <si>
+    <t>Baghlal</t>
+  </si>
+  <si>
+    <t>Elrebbate</t>
+  </si>
+  <si>
+    <t>Achernan</t>
+  </si>
+  <si>
+    <t>Hamdoun</t>
+  </si>
+  <si>
+    <t>Sahli</t>
+  </si>
+  <si>
+    <t>Mrika</t>
+  </si>
+  <si>
+    <t>Ben Hammou</t>
+  </si>
+  <si>
+    <t>Fahim</t>
+  </si>
+  <si>
+    <t>Benkrara</t>
+  </si>
+  <si>
+    <t>Zakya</t>
+  </si>
+  <si>
+    <t>usrname</t>
+  </si>
+  <si>
+    <t>mot de pass</t>
+  </si>
+  <si>
+    <t>A qui</t>
   </si>
 </sst>
 </file>
@@ -111,7 +268,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,8 +276,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -157,6 +320,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -170,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -179,9 +348,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -194,6 +365,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -514,14 +689,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874694C3-6C34-41C1-BAFA-5CBF17469AFF}">
   <dimension ref="C3:L33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="6" max="6" width="39" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12">
+    <row r="3" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D3" s="2">
         <v>0.36458333333333331</v>
       </c>
@@ -535,7 +710,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="3:12">
+    <row r="4" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
@@ -549,7 +724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="3:12">
+    <row r="5" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
@@ -572,7 +747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:12">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
@@ -595,7 +770,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="3:12">
+    <row r="7" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
@@ -616,7 +791,7 @@
       </c>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="3:12">
+    <row r="8" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D8" s="2">
         <v>0.41666666666666602</v>
       </c>
@@ -634,7 +809,7 @@
       </c>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="3:12">
+    <row r="9" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D9" s="2">
         <v>0.42708333333333298</v>
       </c>
@@ -652,7 +827,7 @@
       </c>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="3:12">
+    <row r="10" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D10" s="2">
         <v>0.4375</v>
       </c>
@@ -668,7 +843,7 @@
       </c>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="3:12">
+    <row r="11" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D11" s="2">
         <v>0.44791666666666602</v>
       </c>
@@ -687,7 +862,7 @@
       </c>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="3:12">
+    <row r="12" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D12" s="2">
         <v>0.45833333333333298</v>
       </c>
@@ -706,7 +881,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="3:12">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D13" s="2">
         <v>0.46875</v>
       </c>
@@ -724,7 +899,7 @@
       </c>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="3:12">
+    <row r="14" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D14" s="2">
         <v>0.47916666666666702</v>
       </c>
@@ -742,7 +917,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="3:12">
+    <row r="15" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D15" s="2">
         <v>0.48958333333333298</v>
       </c>
@@ -760,7 +935,7 @@
       </c>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:12">
+    <row r="16" spans="3:12" x14ac:dyDescent="0.35">
       <c r="D16" s="2">
         <v>0.5</v>
       </c>
@@ -778,7 +953,7 @@
       </c>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="4:11">
+    <row r="17" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D17" s="2">
         <v>0.51041666666666596</v>
       </c>
@@ -795,7 +970,7 @@
       </c>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="4:11">
+    <row r="18" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D18" s="2">
         <v>0.52083333333333304</v>
       </c>
@@ -811,7 +986,7 @@
       </c>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="4:11">
+    <row r="19" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D19" s="2">
         <v>0.53125</v>
       </c>
@@ -832,7 +1007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="4:11">
+    <row r="20" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D20" s="2">
         <v>0.54166666666666596</v>
       </c>
@@ -852,7 +1027,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="4:11">
+    <row r="21" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D21" s="2">
         <v>0.55208333333333304</v>
       </c>
@@ -870,7 +1045,7 @@
       </c>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="4:11">
+    <row r="22" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D22" s="2">
         <v>0.5625</v>
       </c>
@@ -888,7 +1063,7 @@
       </c>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="4:11">
+    <row r="23" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D23" s="2">
         <v>0.57291666666666596</v>
       </c>
@@ -906,7 +1081,7 @@
         <v>0.5625</v>
       </c>
     </row>
-    <row r="24" spans="4:11">
+    <row r="24" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D24" s="2">
         <v>0.58333333333333304</v>
       </c>
@@ -924,7 +1099,7 @@
         <v>0.57291666666666596</v>
       </c>
     </row>
-    <row r="25" spans="4:11">
+    <row r="25" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D25" s="2">
         <v>0.593749999999999</v>
       </c>
@@ -941,7 +1116,7 @@
       </c>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="4:11">
+    <row r="26" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D26" s="2">
         <v>0.60416666666666596</v>
       </c>
@@ -960,7 +1135,7 @@
       </c>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="4:11">
+    <row r="27" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D27" s="2">
         <v>0.61458333333333304</v>
       </c>
@@ -978,7 +1153,7 @@
       </c>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="4:11">
+    <row r="28" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D28" s="2">
         <v>0.624999999999999</v>
       </c>
@@ -996,7 +1171,7 @@
       </c>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="4:11">
+    <row r="29" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D29" s="2">
         <v>0.63541666666666596</v>
       </c>
@@ -1014,7 +1189,7 @@
       </c>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="4:11">
+    <row r="30" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D30" s="2">
         <v>0.64583333333333304</v>
       </c>
@@ -1032,7 +1207,7 @@
       </c>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="4:11">
+    <row r="31" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D31" s="2">
         <v>0.656249999999999</v>
       </c>
@@ -1047,7 +1222,7 @@
       </c>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="4:11">
+    <row r="32" spans="4:11" x14ac:dyDescent="0.35">
       <c r="D32" s="2">
         <v>0.66666666666666596</v>
       </c>
@@ -1067,7 +1242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="5:11">
+    <row r="33" spans="5:11" x14ac:dyDescent="0.35">
       <c r="E33" s="2">
         <v>0.66666666666666596</v>
       </c>
@@ -1088,4 +1263,282 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF26148D-B0B8-440E-84ED-5D46A18DD09A}">
+  <dimension ref="D4:K19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="25.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="4:11" x14ac:dyDescent="0.35">
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>